--- a/tiflow-bfarm/main/2.0.0-ballot.2/StructureDefinition-erp-tprescription-medication-dispense.xlsx
+++ b/tiflow-bfarm/main/2.0.0-ballot.2/StructureDefinition-erp-tprescription-medication-dispense.xlsx
@@ -5759,7 +5759,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
